--- a/EmployeeBillableData_7.xlsx
+++ b/EmployeeBillableData_7.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="283">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t>balaji.jadhav@apmosysuat1.com</t>
+  </si>
+  <si>
+    <t>Shadow</t>
   </si>
   <si>
     <t>DEV - TNM - AXISBANK - resource for PHP</t>
@@ -1982,10 +1985,10 @@
         <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="E33" t="s">
-        <v>45</v>
+        <v>145</v>
       </c>
       <c r="F33" t="s">
         <v>15</v>
@@ -1997,7 +2000,7 @@
         <v>16</v>
       </c>
       <c r="I33" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J33" t="s">
         <v>61</v>
@@ -2005,13 +2008,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
@@ -2023,13 +2026,13 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
       </c>
       <c r="I34" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J34" t="s">
         <v>61</v>
@@ -2037,13 +2040,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -2069,13 +2072,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B36" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C36" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -2101,13 +2104,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B37" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C37" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D37" t="s">
         <v>44</v>
@@ -2119,13 +2122,13 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J37" t="s">
         <v>61</v>
@@ -2133,13 +2136,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C38" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2165,13 +2168,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B39" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C39" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -2197,13 +2200,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B40" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C40" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2221,21 +2224,21 @@
         <v>16</v>
       </c>
       <c r="I40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J40" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B41" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D41" t="s">
         <v>44</v>
@@ -2247,13 +2250,13 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J41" t="s">
         <v>61</v>
@@ -2261,13 +2264,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B42" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C42" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -2293,13 +2296,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B43" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C43" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2325,13 +2328,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B44" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C44" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2349,21 +2352,21 @@
         <v>16</v>
       </c>
       <c r="I44" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J44" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B45" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C45" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D45" t="s">
         <v>44</v>
@@ -2381,21 +2384,21 @@
         <v>16</v>
       </c>
       <c r="I45" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J45" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B46" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C46" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -2417,13 +2420,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B47" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C47" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D47" t="s">
         <v>44</v>
@@ -2449,13 +2452,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B48" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C48" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -2481,13 +2484,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C49" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2513,13 +2516,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B50" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -2545,13 +2548,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B51" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C51" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -2577,13 +2580,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B52" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C52" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -2609,13 +2612,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B53" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C53" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2641,13 +2644,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C54" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D54" t="s">
         <v>44</v>
@@ -2673,13 +2676,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B55" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C55" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -2705,13 +2708,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B56" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C56" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D56" t="s">
         <v>44</v>
@@ -2723,13 +2726,13 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
       </c>
       <c r="I56" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J56" t="s">
         <v>61</v>
@@ -2737,13 +2740,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B57" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C57" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -2772,10 +2775,10 @@
         <v>112</v>
       </c>
       <c r="B58" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C58" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -2787,7 +2790,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -2797,13 +2800,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C59" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D59" t="s">
         <v>44</v>
@@ -2815,13 +2818,13 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
       </c>
       <c r="I59" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J59" t="s">
         <v>61</v>
@@ -2829,13 +2832,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B60" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C60" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D60" t="s">
         <v>44</v>
@@ -2861,13 +2864,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -2893,13 +2896,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -2925,13 +2928,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B63" t="s">
         <v>16</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2943,7 +2946,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -2953,13 +2956,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B64" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C64" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -2985,13 +2988,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B65" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D65" t="s">
         <v>44</v>
@@ -3003,13 +3006,13 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
       </c>
       <c r="I65" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J65" t="s">
         <v>61</v>
@@ -3017,13 +3020,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B66" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C66" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D66" t="s">
         <v>44</v>
@@ -3041,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="I66" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J66" t="s">
         <v>61</v>
@@ -3049,13 +3052,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B67" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C67" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D67" t="s">
         <v>44</v>
@@ -3067,13 +3070,13 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J67" t="s">
         <v>61</v>
@@ -3081,13 +3084,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B68" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C68" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D68" t="s">
         <v>44</v>
@@ -3105,7 +3108,7 @@
         <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J68" t="s">
         <v>111</v>
@@ -3113,13 +3116,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3145,13 +3148,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B70" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C70" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D70" t="s">
         <v>44</v>
@@ -3163,13 +3166,13 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
       </c>
       <c r="I70" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J70" t="s">
         <v>61</v>
@@ -3177,13 +3180,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B71" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C71" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3201,21 +3204,21 @@
         <v>16</v>
       </c>
       <c r="I71" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="J71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C72" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -3233,21 +3236,21 @@
         <v>16</v>
       </c>
       <c r="I72" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="J72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B73" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C73" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -3273,13 +3276,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B74" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C74" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -3305,13 +3308,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B75" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C75" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>

--- a/EmployeeBillableData_7.xlsx
+++ b/EmployeeBillableData_7.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="282">
   <si>
     <t>EmployeementId</t>
   </si>
@@ -447,9 +447,6 @@
   </si>
   <si>
     <t>balaji.jadhav@apmosysuat1.com</t>
-  </si>
-  <si>
-    <t>Shadow</t>
   </si>
   <si>
     <t>DEV - TNM - AXISBANK - resource for PHP</t>
@@ -1985,22 +1982,22 @@
         <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F33" t="s">
+        <v>15</v>
+      </c>
+      <c r="G33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
         <v>145</v>
-      </c>
-      <c r="F33" t="s">
-        <v>15</v>
-      </c>
-      <c r="G33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H33" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" t="s">
-        <v>146</v>
       </c>
       <c r="J33" t="s">
         <v>61</v>
@@ -2008,13 +2005,13 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" t="s">
         <v>147</v>
       </c>
-      <c r="B34" t="s">
+      <c r="C34" t="s">
         <v>148</v>
-      </c>
-      <c r="C34" t="s">
-        <v>149</v>
       </c>
       <c r="D34" t="s">
         <v>44</v>
@@ -2026,13 +2023,13 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
+        <v>149</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
         <v>150</v>
-      </c>
-      <c r="H34" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" t="s">
-        <v>151</v>
       </c>
       <c r="J34" t="s">
         <v>61</v>
@@ -2040,13 +2037,13 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>151</v>
+      </c>
+      <c r="B35" t="s">
         <v>152</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" t="s">
         <v>153</v>
-      </c>
-      <c r="C35" t="s">
-        <v>154</v>
       </c>
       <c r="D35" t="s">
         <v>13</v>
@@ -2072,13 +2069,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
+        <v>154</v>
+      </c>
+      <c r="B36" t="s">
         <v>155</v>
       </c>
-      <c r="B36" t="s">
+      <c r="C36" t="s">
         <v>156</v>
-      </c>
-      <c r="C36" t="s">
-        <v>157</v>
       </c>
       <c r="D36" t="s">
         <v>13</v>
@@ -2104,13 +2101,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
+        <v>157</v>
+      </c>
+      <c r="B37" t="s">
         <v>158</v>
       </c>
-      <c r="B37" t="s">
+      <c r="C37" t="s">
         <v>159</v>
-      </c>
-      <c r="C37" t="s">
-        <v>160</v>
       </c>
       <c r="D37" t="s">
         <v>44</v>
@@ -2122,13 +2119,13 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
+        <v>149</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
         <v>150</v>
-      </c>
-      <c r="H37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s">
-        <v>151</v>
       </c>
       <c r="J37" t="s">
         <v>61</v>
@@ -2136,13 +2133,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
+        <v>160</v>
+      </c>
+      <c r="B38" t="s">
         <v>161</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>162</v>
-      </c>
-      <c r="C38" t="s">
-        <v>163</v>
       </c>
       <c r="D38" t="s">
         <v>13</v>
@@ -2168,13 +2165,13 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>163</v>
+      </c>
+      <c r="B39" t="s">
         <v>164</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>165</v>
-      </c>
-      <c r="C39" t="s">
-        <v>166</v>
       </c>
       <c r="D39" t="s">
         <v>13</v>
@@ -2200,13 +2197,13 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>166</v>
+      </c>
+      <c r="B40" t="s">
         <v>167</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>168</v>
-      </c>
-      <c r="C40" t="s">
-        <v>169</v>
       </c>
       <c r="D40" t="s">
         <v>13</v>
@@ -2224,21 +2221,21 @@
         <v>16</v>
       </c>
       <c r="I40" t="s">
+        <v>169</v>
+      </c>
+      <c r="J40" t="s">
         <v>170</v>
-      </c>
-      <c r="J40" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
+        <v>171</v>
+      </c>
+      <c r="B41" t="s">
         <v>172</v>
       </c>
-      <c r="B41" t="s">
+      <c r="C41" t="s">
         <v>173</v>
-      </c>
-      <c r="C41" t="s">
-        <v>174</v>
       </c>
       <c r="D41" t="s">
         <v>44</v>
@@ -2250,13 +2247,13 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
       </c>
       <c r="I41" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J41" t="s">
         <v>61</v>
@@ -2264,13 +2261,13 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
+        <v>175</v>
+      </c>
+      <c r="B42" t="s">
         <v>176</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
         <v>177</v>
-      </c>
-      <c r="C42" t="s">
-        <v>178</v>
       </c>
       <c r="D42" t="s">
         <v>13</v>
@@ -2296,13 +2293,13 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>178</v>
+      </c>
+      <c r="B43" t="s">
         <v>179</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>180</v>
-      </c>
-      <c r="C43" t="s">
-        <v>181</v>
       </c>
       <c r="D43" t="s">
         <v>13</v>
@@ -2328,13 +2325,13 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
+        <v>181</v>
+      </c>
+      <c r="B44" t="s">
         <v>182</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>183</v>
-      </c>
-      <c r="C44" t="s">
-        <v>184</v>
       </c>
       <c r="D44" t="s">
         <v>13</v>
@@ -2352,21 +2349,21 @@
         <v>16</v>
       </c>
       <c r="I44" t="s">
+        <v>184</v>
+      </c>
+      <c r="J44" t="s">
         <v>185</v>
-      </c>
-      <c r="J44" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
+        <v>186</v>
+      </c>
+      <c r="B45" t="s">
         <v>187</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
         <v>188</v>
-      </c>
-      <c r="C45" t="s">
-        <v>189</v>
       </c>
       <c r="D45" t="s">
         <v>44</v>
@@ -2384,21 +2381,21 @@
         <v>16</v>
       </c>
       <c r="I45" t="s">
+        <v>189</v>
+      </c>
+      <c r="J45" t="s">
         <v>190</v>
-      </c>
-      <c r="J45" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
+        <v>191</v>
+      </c>
+      <c r="B46" t="s">
         <v>192</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>193</v>
-      </c>
-      <c r="C46" t="s">
-        <v>194</v>
       </c>
       <c r="D46" t="s">
         <v>13</v>
@@ -2420,13 +2417,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
+        <v>194</v>
+      </c>
+      <c r="B47" t="s">
         <v>195</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>196</v>
-      </c>
-      <c r="C47" t="s">
-        <v>197</v>
       </c>
       <c r="D47" t="s">
         <v>44</v>
@@ -2452,13 +2449,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
+        <v>197</v>
+      </c>
+      <c r="B48" t="s">
         <v>198</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>199</v>
-      </c>
-      <c r="C48" t="s">
-        <v>200</v>
       </c>
       <c r="D48" t="s">
         <v>13</v>
@@ -2484,13 +2481,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
+        <v>200</v>
+      </c>
+      <c r="B49" t="s">
         <v>201</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>202</v>
-      </c>
-      <c r="C49" t="s">
-        <v>203</v>
       </c>
       <c r="D49" t="s">
         <v>13</v>
@@ -2516,13 +2513,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" t="s">
         <v>204</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>205</v>
-      </c>
-      <c r="C50" t="s">
-        <v>206</v>
       </c>
       <c r="D50" t="s">
         <v>13</v>
@@ -2548,13 +2545,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
+        <v>206</v>
+      </c>
+      <c r="B51" t="s">
         <v>207</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>208</v>
-      </c>
-      <c r="C51" t="s">
-        <v>209</v>
       </c>
       <c r="D51" t="s">
         <v>13</v>
@@ -2580,13 +2577,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
+        <v>209</v>
+      </c>
+      <c r="B52" t="s">
         <v>210</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>211</v>
-      </c>
-      <c r="C52" t="s">
-        <v>212</v>
       </c>
       <c r="D52" t="s">
         <v>13</v>
@@ -2612,13 +2609,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" t="s">
         <v>213</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>214</v>
-      </c>
-      <c r="C53" t="s">
-        <v>215</v>
       </c>
       <c r="D53" t="s">
         <v>13</v>
@@ -2644,13 +2641,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
+        <v>215</v>
+      </c>
+      <c r="B54" t="s">
         <v>216</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C54" t="s">
         <v>217</v>
-      </c>
-      <c r="C54" t="s">
-        <v>218</v>
       </c>
       <c r="D54" t="s">
         <v>44</v>
@@ -2676,13 +2673,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
+        <v>218</v>
+      </c>
+      <c r="B55" t="s">
         <v>219</v>
       </c>
-      <c r="B55" t="s">
+      <c r="C55" t="s">
         <v>220</v>
-      </c>
-      <c r="C55" t="s">
-        <v>221</v>
       </c>
       <c r="D55" t="s">
         <v>13</v>
@@ -2708,13 +2705,13 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
+        <v>221</v>
+      </c>
+      <c r="B56" t="s">
         <v>222</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>223</v>
-      </c>
-      <c r="C56" t="s">
-        <v>224</v>
       </c>
       <c r="D56" t="s">
         <v>44</v>
@@ -2726,13 +2723,13 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
+        <v>149</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
         <v>150</v>
-      </c>
-      <c r="H56" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" t="s">
-        <v>151</v>
       </c>
       <c r="J56" t="s">
         <v>61</v>
@@ -2740,13 +2737,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
+        <v>224</v>
+      </c>
+      <c r="B57" t="s">
         <v>225</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>226</v>
-      </c>
-      <c r="C57" t="s">
-        <v>227</v>
       </c>
       <c r="D57" t="s">
         <v>13</v>
@@ -2775,10 +2772,10 @@
         <v>112</v>
       </c>
       <c r="B58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C58" t="s">
         <v>228</v>
-      </c>
-      <c r="C58" t="s">
-        <v>229</v>
       </c>
       <c r="D58" t="s">
         <v>13</v>
@@ -2790,7 +2787,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -2800,13 +2797,13 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>230</v>
+      </c>
+      <c r="B59" t="s">
+        <v>174</v>
+      </c>
+      <c r="C59" t="s">
         <v>231</v>
-      </c>
-      <c r="B59" t="s">
-        <v>175</v>
-      </c>
-      <c r="C59" t="s">
-        <v>232</v>
       </c>
       <c r="D59" t="s">
         <v>44</v>
@@ -2818,13 +2815,13 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
+        <v>149</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s">
         <v>150</v>
-      </c>
-      <c r="H59" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" t="s">
-        <v>151</v>
       </c>
       <c r="J59" t="s">
         <v>61</v>
@@ -2832,13 +2829,13 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
+        <v>232</v>
+      </c>
+      <c r="B60" t="s">
         <v>233</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>234</v>
-      </c>
-      <c r="C60" t="s">
-        <v>235</v>
       </c>
       <c r="D60" t="s">
         <v>44</v>
@@ -2864,13 +2861,13 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
+        <v>235</v>
+      </c>
+      <c r="B61" t="s">
+        <v>23</v>
+      </c>
+      <c r="C61" t="s">
         <v>236</v>
-      </c>
-      <c r="B61" t="s">
-        <v>23</v>
-      </c>
-      <c r="C61" t="s">
-        <v>237</v>
       </c>
       <c r="D61" t="s">
         <v>13</v>
@@ -2896,13 +2893,13 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
+        <v>237</v>
+      </c>
+      <c r="B62" t="s">
         <v>238</v>
       </c>
-      <c r="B62" t="s">
+      <c r="C62" t="s">
         <v>239</v>
-      </c>
-      <c r="C62" t="s">
-        <v>240</v>
       </c>
       <c r="D62" t="s">
         <v>13</v>
@@ -2928,13 +2925,13 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
+        <v>240</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="s">
         <v>241</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="s">
-        <v>242</v>
       </c>
       <c r="D63" t="s">
         <v>13</v>
@@ -2946,7 +2943,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -2956,13 +2953,13 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" t="s">
         <v>243</v>
       </c>
-      <c r="B64" t="s">
+      <c r="C64" t="s">
         <v>244</v>
-      </c>
-      <c r="C64" t="s">
-        <v>245</v>
       </c>
       <c r="D64" t="s">
         <v>13</v>
@@ -2988,13 +2985,13 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
+        <v>245</v>
+      </c>
+      <c r="B65" t="s">
         <v>246</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>247</v>
-      </c>
-      <c r="C65" t="s">
-        <v>248</v>
       </c>
       <c r="D65" t="s">
         <v>44</v>
@@ -3006,13 +3003,13 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
       </c>
       <c r="I65" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J65" t="s">
         <v>61</v>
@@ -3020,13 +3017,13 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
+        <v>248</v>
+      </c>
+      <c r="B66" t="s">
         <v>249</v>
       </c>
-      <c r="B66" t="s">
+      <c r="C66" t="s">
         <v>250</v>
-      </c>
-      <c r="C66" t="s">
-        <v>251</v>
       </c>
       <c r="D66" t="s">
         <v>44</v>
@@ -3044,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="I66" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J66" t="s">
         <v>61</v>
@@ -3052,13 +3049,13 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
+        <v>251</v>
+      </c>
+      <c r="B67" t="s">
         <v>252</v>
       </c>
-      <c r="B67" t="s">
+      <c r="C67" t="s">
         <v>253</v>
-      </c>
-      <c r="C67" t="s">
-        <v>254</v>
       </c>
       <c r="D67" t="s">
         <v>44</v>
@@ -3070,13 +3067,13 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
       </c>
       <c r="I67" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J67" t="s">
         <v>61</v>
@@ -3084,13 +3081,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
+        <v>254</v>
+      </c>
+      <c r="B68" t="s">
         <v>255</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>256</v>
-      </c>
-      <c r="C68" t="s">
-        <v>257</v>
       </c>
       <c r="D68" t="s">
         <v>44</v>
@@ -3108,7 +3105,7 @@
         <v>16</v>
       </c>
       <c r="I68" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J68" t="s">
         <v>111</v>
@@ -3116,13 +3113,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B69" t="s">
         <v>50</v>
       </c>
       <c r="C69" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D69" t="s">
         <v>13</v>
@@ -3148,13 +3145,13 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
+        <v>260</v>
+      </c>
+      <c r="B70" t="s">
         <v>261</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>262</v>
-      </c>
-      <c r="C70" t="s">
-        <v>263</v>
       </c>
       <c r="D70" t="s">
         <v>44</v>
@@ -3166,13 +3163,13 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
       </c>
       <c r="I70" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J70" t="s">
         <v>61</v>
@@ -3180,13 +3177,13 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
+        <v>263</v>
+      </c>
+      <c r="B71" t="s">
         <v>264</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>265</v>
-      </c>
-      <c r="C71" t="s">
-        <v>266</v>
       </c>
       <c r="D71" t="s">
         <v>13</v>
@@ -3204,21 +3201,21 @@
         <v>16</v>
       </c>
       <c r="I71" t="s">
+        <v>266</v>
+      </c>
+      <c r="J71" t="s">
         <v>267</v>
-      </c>
-      <c r="J71" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" t="s">
         <v>269</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>270</v>
-      </c>
-      <c r="C72" t="s">
-        <v>271</v>
       </c>
       <c r="D72" t="s">
         <v>13</v>
@@ -3236,21 +3233,21 @@
         <v>16</v>
       </c>
       <c r="I72" t="s">
+        <v>271</v>
+      </c>
+      <c r="J72" t="s">
         <v>272</v>
-      </c>
-      <c r="J72" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
+        <v>273</v>
+      </c>
+      <c r="B73" t="s">
         <v>274</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>275</v>
-      </c>
-      <c r="C73" t="s">
-        <v>276</v>
       </c>
       <c r="D73" t="s">
         <v>13</v>
@@ -3276,13 +3273,13 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
+        <v>276</v>
+      </c>
+      <c r="B74" t="s">
         <v>277</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>278</v>
-      </c>
-      <c r="C74" t="s">
-        <v>279</v>
       </c>
       <c r="D74" t="s">
         <v>13</v>
@@ -3308,13 +3305,13 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
+        <v>279</v>
+      </c>
+      <c r="B75" t="s">
         <v>280</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>281</v>
-      </c>
-      <c r="C75" t="s">
-        <v>282</v>
       </c>
       <c r="D75" t="s">
         <v>13</v>
